--- a/Questions.xlsx
+++ b/Questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shubham\Desktop\everything\GIt Work\Data_Structures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2193EED7-59DA-444C-9E3A-1411F0F476D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10EB0532-0967-4DC7-A01F-BB061107CE70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="13">
   <si>
     <t>Sr no</t>
   </si>
@@ -61,6 +61,9 @@
   </si>
   <si>
     <t>Smallest and second smallest</t>
+  </si>
+  <si>
+    <t>Second largest</t>
   </si>
 </sst>
 </file>
@@ -381,11 +384,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
-    <col min="2" max="2" width="19.33203125" customWidth="1"/>
+    <col min="2" max="2" width="36.6640625" customWidth="1"/>
     <col min="3" max="3" width="17.44140625" style="1" customWidth="1"/>
     <col min="4" max="4" width="11.33203125" style="1" customWidth="1"/>
     <col min="5" max="5" width="12.109375" style="1" customWidth="1"/>
@@ -449,6 +452,23 @@
         <v>8</v>
       </c>
     </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Questions.xlsx
+++ b/Questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shubham\Desktop\everything\GIt Work\Data_Structures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10EB0532-0967-4DC7-A01F-BB061107CE70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42B99637-D455-4866-96A1-1ECAF3AA1D4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="20">
   <si>
     <t>Sr no</t>
   </si>
@@ -64,6 +64,27 @@
   </si>
   <si>
     <t>Second largest</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Remove Duplicates</t>
+  </si>
+  <si>
+    <t>Leetcode</t>
+  </si>
+  <si>
+    <t>Array is Sorted</t>
+  </si>
+  <si>
+    <t>Missing number</t>
+  </si>
+  <si>
+    <t>Consecutives Ones</t>
   </si>
 </sst>
 </file>
@@ -384,7 +405,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
@@ -451,6 +472,9 @@
       <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="F3" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
@@ -467,6 +491,80 @@
       </c>
       <c r="E4" s="1" t="s">
         <v>8</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/Questions.xlsx
+++ b/Questions.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shubham\Desktop\everything\GIt Work\Data_Structures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42B99637-D455-4866-96A1-1ECAF3AA1D4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC8F9571-7F61-4C87-900B-BE41409D36A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="21">
   <si>
     <t>Sr no</t>
   </si>
@@ -85,6 +85,9 @@
   </si>
   <si>
     <t>Consecutives Ones</t>
+  </si>
+  <si>
+    <t>two sum</t>
   </si>
 </sst>
 </file>
@@ -405,7 +408,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
@@ -567,6 +570,14 @@
         <v>16</v>
       </c>
     </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Questions.xlsx
+++ b/Questions.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shubham\Desktop\everything\GIt Work\Data_Structures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC8F9571-7F61-4C87-900B-BE41409D36A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD81770F-F0A7-42C0-8004-2FDC5A0206B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="26">
   <si>
     <t>Sr no</t>
   </si>
@@ -87,7 +87,22 @@
     <t>Consecutives Ones</t>
   </si>
   <si>
-    <t>two sum</t>
+    <t>Love Babbar</t>
+  </si>
+  <si>
+    <t>Find Duplicate number</t>
+  </si>
+  <si>
+    <t>Any algo or pattern</t>
+  </si>
+  <si>
+    <t>Floyds Cycle Detection</t>
+  </si>
+  <si>
+    <t>Left rotate array by one place</t>
+  </si>
+  <si>
+    <t>Left rotate array by k places</t>
   </si>
 </sst>
 </file>
@@ -408,7 +423,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
@@ -417,9 +432,10 @@
     <col min="4" max="4" width="11.33203125" style="1" customWidth="1"/>
     <col min="5" max="5" width="12.109375" style="1" customWidth="1"/>
     <col min="6" max="6" width="8.88671875" style="1"/>
+    <col min="7" max="7" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -438,8 +454,11 @@
       <c r="F1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -459,7 +478,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -479,7 +498,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -499,7 +518,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -519,7 +538,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -536,7 +555,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -553,7 +572,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -570,12 +589,72 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>20</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C12" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
